--- a/public/exports-with-coowners/29189854.xlsx
+++ b/public/exports-with-coowners/29189854.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/29189854.xlsx
+++ b/public/exports-with-coowners/29189854.xlsx
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museum Sønderjylland</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1541,50 +1541,50 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">H P Hanssens Gade 33</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776368</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J21">
-        <v>839</v>
+        <v>534</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178681</t>
+          <t xml:space="preserve">311358212</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2029-02-06</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1616,40 +1616,40 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Skelbækvej 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5777441</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>534</v>
+        <v>13747</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358212</t>
+          <t xml:space="preserve">311384248</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-06</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1691,40 +1691,40 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelbækvej 2</t>
+          <t xml:space="preserve">Valdemarsgade 11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777441</t>
+          <t xml:space="preserve">10006074</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J23">
-        <v>13747</v>
+        <v>381</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384248</t>
+          <t xml:space="preserve">311385901</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2029-07-02</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1766,40 +1766,40 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsgade 11</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">10006074</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>381</v>
+        <v>7580</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385901</t>
+          <t xml:space="preserve">311434534</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-02</t>
+          <t xml:space="preserve">2030-04-27</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Kirkegade 23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5250298</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="J25">
-        <v>7580</v>
+        <v>626</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434534</t>
+          <t xml:space="preserve">311498610</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-27</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 23</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250298</t>
+          <t xml:space="preserve">5777076</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="J26">
-        <v>626</v>
+        <v>452</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498610</t>
+          <t xml:space="preserve">311522368</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
+          <t xml:space="preserve">Hovedgaden 78</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777076</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J27">
-        <v>452</v>
+        <v>1439</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522368</t>
+          <t xml:space="preserve">311522367</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J28">
-        <v>1439</v>
+        <v>1390</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 78</t>
+          <t xml:space="preserve">Nørreagervej 45</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2156,11 +2156,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J29">
-        <v>1390</v>
+        <v>3702</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreagervej 45</t>
+          <t xml:space="preserve">Tinglev Midt 2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J30">
-        <v>3702</v>
+        <v>2743</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522367</t>
+          <t xml:space="preserve">311522375</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 2</t>
+          <t xml:space="preserve">Tinglev Midt 4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2306,15 +2306,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J31">
-        <v>2743</v>
+        <v>1267</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522375</t>
+          <t xml:space="preserve">311522371</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 4</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2381,25 +2381,25 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J32">
-        <v>1267</v>
+        <v>847</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522371</t>
+          <t xml:space="preserve">311578480</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Tinglev Midt 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J33">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578480</t>
+          <t xml:space="preserve">311578481</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 2</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2531,15 +2531,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J34">
-        <v>847</v>
+        <v>602</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578481</t>
+          <t xml:space="preserve">311578773</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-13</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,40 +2591,40 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Østermarkvej 1P</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J35">
-        <v>602</v>
+        <v>555</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578773</t>
+          <t xml:space="preserve">311601866</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,40 +2666,40 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1P</t>
+          <t xml:space="preserve">Kalveknækket 47</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5262648</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J36">
-        <v>555</v>
+        <v>2330</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601866</t>
+          <t xml:space="preserve">311644250</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 47</t>
+          <t xml:space="preserve">Molevej 18A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262648</t>
+          <t xml:space="preserve">5262575</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>2330</v>
+        <v>336</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644250</t>
+          <t xml:space="preserve">311650394</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,17 +2816,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molevej 18A</t>
+          <t xml:space="preserve">Smedefod 4B</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262575</t>
+          <t xml:space="preserve">5248731</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650394</t>
+          <t xml:space="preserve">311650397</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 4B</t>
+          <t xml:space="preserve">Åbovej 12A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248731</t>
+          <t xml:space="preserve">312951, 312952</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>316</v>
+        <v>1169</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650397</t>
+          <t xml:space="preserve">311650395</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 12A</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">312951, 312952</t>
+          <t xml:space="preserve">100044523</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>1169</v>
+        <v>334</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650395</t>
+          <t xml:space="preserve">311653972</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,40 +3041,40 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044523</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J41">
-        <v>334</v>
+        <v>778</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653972</t>
+          <t xml:space="preserve">311654332</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-13</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3131,15 +3131,15 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J42">
-        <v>778</v>
+        <v>665</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654332</t>
+          <t xml:space="preserve">311654333</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3191,40 +3191,40 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Kalveknækket 45A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5262778</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J43">
-        <v>665</v>
+        <v>558</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654333</t>
+          <t xml:space="preserve">311654619</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 45A</t>
+          <t xml:space="preserve">Flensborgvej 9B</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,20 +3276,20 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262778</t>
+          <t xml:space="preserve">5263423</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>558</v>
+        <v>348</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654619</t>
+          <t xml:space="preserve">311661161</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flensborgvej 9B</t>
+          <t xml:space="preserve">Mads Clausens Vej 130</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263423</t>
+          <t xml:space="preserve">5243879</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>348</v>
+        <v>814</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661161</t>
+          <t xml:space="preserve">311661163</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 130</t>
+          <t xml:space="preserve">Smedefod 10A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243879</t>
+          <t xml:space="preserve">5248692</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J46">
-        <v>814</v>
+        <v>3970</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661163</t>
+          <t xml:space="preserve">311661158</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3491,30 +3491,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 10A</t>
+          <t xml:space="preserve">Tværvejen 4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248692</t>
+          <t xml:space="preserve">5242741</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>3970</v>
+        <v>338</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661158</t>
+          <t xml:space="preserve">311661169</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvejen 4</t>
+          <t xml:space="preserve">Hovedgaden 78</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242741</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="J48">
-        <v>338</v>
+        <v>1466</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661169</t>
+          <t xml:space="preserve">311661648</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 78</t>
+          <t xml:space="preserve">Hovedgaden 82</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5242835</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3660,11 +3660,11 @@
         </is>
       </c>
       <c r="J49">
-        <v>1466</v>
+        <v>357</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661648</t>
+          <t xml:space="preserve">311661649</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,17 +3716,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 82</t>
+          <t xml:space="preserve">Nørrekær 15</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242835</t>
+          <t xml:space="preserve">9073631</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3735,11 +3735,11 @@
         </is>
       </c>
       <c r="J50">
-        <v>357</v>
+        <v>3104</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661649</t>
+          <t xml:space="preserve">311661636</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrekær 15</t>
+          <t xml:space="preserve">Skolegade 12A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073631</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3810,11 +3810,11 @@
         </is>
       </c>
       <c r="J51">
-        <v>3104</v>
+        <v>1798</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661636</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12A</t>
+          <t xml:space="preserve">Skolegade 12B</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3881,11 +3881,11 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>1798</v>
+        <v>516</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12B</t>
+          <t xml:space="preserve">Skolegade 12C</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3956,15 +3956,15 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J53">
-        <v>516</v>
+        <v>409</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661642</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12C</t>
+          <t xml:space="preserve">Åbovej 27A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">5235664</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>409</v>
+        <v>319</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661642</t>
+          <t xml:space="preserve">311661637</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 27A</t>
+          <t xml:space="preserve">Sønderskovvej 25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235664</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="J55">
-        <v>319</v>
+        <v>829</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661637</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 25</t>
+          <t xml:space="preserve">Sønderskovvej 27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4181,11 +4181,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J56">
-        <v>829</v>
+        <v>364</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,30 +4241,30 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 27</t>
+          <t xml:space="preserve">Engløkke 30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">5235995</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J57">
-        <v>364</v>
+        <v>4022</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661950</t>
+          <t xml:space="preserve">311667969</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,17 +4316,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engløkke 30</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235995</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,16 +4335,16 @@
         </is>
       </c>
       <c r="J58">
-        <v>4022</v>
+        <v>1216</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667969</t>
+          <t xml:space="preserve">311667988</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4406,20 +4406,20 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J59">
-        <v>1216</v>
+        <v>524</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667988</t>
+          <t xml:space="preserve">311667989</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
+          <t xml:space="preserve">Nørreagervej 58</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">5243876</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>524</v>
+        <v>1027</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667989</t>
+          <t xml:space="preserve">311668049</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreagervej 58</t>
+          <t xml:space="preserve">Østermarkvej 1A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243876</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>1027</v>
+        <v>406</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668049</t>
+          <t xml:space="preserve">311668436</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1A</t>
+          <t xml:space="preserve">Østermarkvej 1B</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4631,15 +4631,15 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J62">
-        <v>406</v>
+        <v>935</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668436</t>
+          <t xml:space="preserve">311668438</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1B</t>
+          <t xml:space="preserve">Bytoften 13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5274226</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J63">
-        <v>935</v>
+        <v>854</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668438</t>
+          <t xml:space="preserve">311670155</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 13</t>
+          <t xml:space="preserve">Klostervang 46</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274226</t>
+          <t xml:space="preserve">5270632</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>854</v>
+        <v>608</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670155</t>
+          <t xml:space="preserve">311670156</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4841,30 +4841,30 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervang 46</t>
+          <t xml:space="preserve">Kobbermøllevej 50A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270632</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J65">
-        <v>608</v>
+        <v>1072</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670156</t>
+          <t xml:space="preserve">311670165</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50A</t>
+          <t xml:space="preserve">Kobbermøllevej 50B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4931,20 +4931,20 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J66">
-        <v>1072</v>
+        <v>408</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670165</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50B</t>
+          <t xml:space="preserve">Kobbermøllevej 50C</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J67">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50C</t>
+          <t xml:space="preserve">Kobbermøllevej 50D</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J68">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50D</t>
+          <t xml:space="preserve">Kobbermøllevej 50E</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J69">
@@ -5216,35 +5216,35 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50E</t>
+          <t xml:space="preserve">Ravsted Skolegade 16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">9345395</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J70">
-        <v>408</v>
+        <v>267</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670238</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 16</t>
+          <t xml:space="preserve">Ravsted Skolegade 18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5306,15 +5306,15 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>267</v>
+        <v>2157</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670238</t>
+          <t xml:space="preserve">311670236</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 18</t>
+          <t xml:space="preserve">Varnæs Kirkevej 15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345395</t>
+          <t xml:space="preserve">5274894</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,16 +5385,16 @@
         </is>
       </c>
       <c r="J72">
-        <v>2157</v>
+        <v>2071</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670236</t>
+          <t xml:space="preserve">311670153</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varnæs Kirkevej 15</t>
+          <t xml:space="preserve">Gammel Søndergade 20A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274894</t>
+          <t xml:space="preserve">5248471</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="J73">
-        <v>2071</v>
+        <v>358</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670153</t>
+          <t xml:space="preserve">311670600</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5531,15 +5531,15 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J74">
-        <v>358</v>
+        <v>862</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670600</t>
+          <t xml:space="preserve">311670599</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20A</t>
+          <t xml:space="preserve">Gammel Søndergade 20L</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248471</t>
+          <t xml:space="preserve">8040385</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J75">
-        <v>862</v>
+        <v>470</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670599</t>
+          <t xml:space="preserve">311670603</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5666,30 +5666,30 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20L</t>
+          <t xml:space="preserve">Slogsherredsvej 27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040385</t>
+          <t xml:space="preserve">9120321</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>470</v>
+        <v>2095</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670603</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J77">
-        <v>2095</v>
+        <v>806</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J78">
-        <v>806</v>
+        <v>2646</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Domea Syd</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5891,40 +5891,40 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 27</t>
+          <t xml:space="preserve">Rise Bygade 50</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120321</t>
+          <t xml:space="preserve">312318, 312319</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J79">
-        <v>2646</v>
+        <v>926</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311678544</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-12</t>
+          <t xml:space="preserve">2033-05-03</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 50</t>
+          <t xml:space="preserve">Rise Bygade 52</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J80">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 52</t>
+          <t xml:space="preserve">Rise Bygade 54</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6056,11 +6056,11 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J81">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 54</t>
+          <t xml:space="preserve">Rise Bygade 56</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J82">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 56</t>
+          <t xml:space="preserve">Rise Bygade 58</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J83">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 58</t>
+          <t xml:space="preserve">Rise Bygade 60</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6281,11 +6281,11 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J84">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 60</t>
+          <t xml:space="preserve">Rise Bygade 62</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6356,11 +6356,11 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J85">
-        <v>963</v>
+        <v>927</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6401,12 +6401,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domea Syd</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6416,40 +6416,40 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 62</t>
+          <t xml:space="preserve">Bovvej 2A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">312318, 312319</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J86">
-        <v>927</v>
+        <v>314</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678544</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-03</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2A</t>
+          <t xml:space="preserve">Bovvej 2B</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6506,11 +6506,11 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J87">
-        <v>314</v>
+        <v>510</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6581,11 +6581,11 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
-        <v>510</v>
+        <v>268</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2B</t>
+          <t xml:space="preserve">Bovvej 4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5260034</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>268</v>
+        <v>1438</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311679002</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 4</t>
+          <t xml:space="preserve">Padborgvej 55B</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260034</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J90">
-        <v>1438</v>
+        <v>1419</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679002</t>
+          <t xml:space="preserve">311679338</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55B</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5259724</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>1419</v>
+        <v>438</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679338</t>
+          <t xml:space="preserve">311680033</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Jernbanegade 36A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259724</t>
+          <t xml:space="preserve">5260026</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6885,11 +6885,11 @@
         </is>
       </c>
       <c r="J92">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680033</t>
+          <t xml:space="preserve">311680035</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 36A</t>
+          <t xml:space="preserve">Lejrvejen 13</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260026</t>
+          <t xml:space="preserve">737452, 9069252</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="J93">
-        <v>415</v>
+        <v>629</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680035</t>
+          <t xml:space="preserve">311680150</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 13</t>
+          <t xml:space="preserve">Padborgvej 20A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">737452, 9069252</t>
+          <t xml:space="preserve">9410204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>629</v>
+        <v>1971</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680150</t>
+          <t xml:space="preserve">311691896</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20A</t>
+          <t xml:space="preserve">Padborgvej 20B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7106,20 +7106,20 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J95">
-        <v>1971</v>
+        <v>1232</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691896</t>
+          <t xml:space="preserve">311691894</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20B</t>
+          <t xml:space="preserve">Padborgvej 20C</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7181,11 +7181,11 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J96">
-        <v>1232</v>
+        <v>451</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20C</t>
+          <t xml:space="preserve">Padborgvej 20D</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>451</v>
+        <v>573</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20D</t>
+          <t xml:space="preserve">Plantagevej 2B</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410204</t>
+          <t xml:space="preserve">5260531</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J98">
-        <v>573</v>
+        <v>1842</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691894</t>
+          <t xml:space="preserve">311696895</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-30</t>
+          <t xml:space="preserve">2033-07-27</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2B</t>
+          <t xml:space="preserve">Kempesteens Vej 70</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260531</t>
+          <t xml:space="preserve">5260533</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7410,11 +7410,11 @@
         </is>
       </c>
       <c r="J99">
-        <v>1842</v>
+        <v>492</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696895</t>
+          <t xml:space="preserve">311706365</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-27</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">BoligSyd</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7466,40 +7466,40 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kempesteens Vej 70</t>
+          <t xml:space="preserve">Mejerihaven 1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260533</t>
+          <t xml:space="preserve">312368, 312369</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J100">
-        <v>492</v>
+        <v>450</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706365</t>
+          <t xml:space="preserve">311707108</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">BoligSyd</t>
+          <t xml:space="preserve">KOLSTRUP BOLIGFORENING</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerihaven 1</t>
+          <t xml:space="preserve">Lergård 100</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">312368, 312369</t>
+          <t xml:space="preserve">421261, 421262</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J101">
-        <v>450</v>
+        <v>1074</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707108</t>
+          <t xml:space="preserve">311707964</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 100</t>
+          <t xml:space="preserve">Lergård 102</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J102">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 102</t>
+          <t xml:space="preserve">Lergård 104</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J103">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">KOLSTRUP BOLIGFORENING</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 104</t>
+          <t xml:space="preserve">Lergård 88</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,20 +7776,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">421261, 421262</t>
+          <t xml:space="preserve">311019</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J104">
-        <v>1074</v>
+        <v>815</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707964</t>
+          <t xml:space="preserve">311717620</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 88</t>
+          <t xml:space="preserve">Funkevej 9A</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311019</t>
+          <t xml:space="preserve">5254271</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="J105">
-        <v>815</v>
+        <v>415</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717620</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7931,15 +7931,15 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J106">
-        <v>415</v>
+        <v>1536</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763724</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8006,15 +8006,15 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J107">
-        <v>1536</v>
+        <v>452</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763724</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funkevej 9A</t>
+          <t xml:space="preserve">Gasværksvej 20</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254271</t>
+          <t xml:space="preserve">5775323</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>452</v>
+        <v>2574</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763728</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 20</t>
+          <t xml:space="preserve">Gråstenvej 1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,20 +8151,20 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775323</t>
+          <t xml:space="preserve">7747263</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J109">
-        <v>2574</v>
+        <v>2087</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763728</t>
+          <t xml:space="preserve">311763695</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 1</t>
+          <t xml:space="preserve">Gråstenvej 12</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">7747263</t>
+          <t xml:space="preserve">9303236</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>2087</v>
+        <v>677</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763695</t>
+          <t xml:space="preserve">311763696</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,17 +8291,17 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 12</t>
+          <t xml:space="preserve">Grønningen 4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">9303236</t>
+          <t xml:space="preserve">5255617</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>677</v>
+        <v>278</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763696</t>
+          <t xml:space="preserve">311763693</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,35 +8366,35 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 4</t>
+          <t xml:space="preserve">Lavgade 30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255617</t>
+          <t xml:space="preserve">5775595</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J112">
-        <v>278</v>
+        <v>2589</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763693</t>
+          <t xml:space="preserve">311763897</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavgade 30</t>
+          <t xml:space="preserve">Nygade 20</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8456,20 +8456,20 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J113">
-        <v>2589</v>
+        <v>3338</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763897</t>
+          <t xml:space="preserve">311763900</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Total-Tjek</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -8516,35 +8516,35 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 20</t>
+          <t xml:space="preserve">Strandvej 10</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775595</t>
+          <t xml:space="preserve">5268254</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>3338</v>
+        <v>1015</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763900</t>
+          <t xml:space="preserve">311763726</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total-Tjek</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268254</t>
+          <t xml:space="preserve">5268269</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J115">
-        <v>1015</v>
+        <v>262</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763726</t>
+          <t xml:space="preserve">311763735</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8681,11 +8681,11 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J116">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8741,30 +8741,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 10</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268269</t>
+          <t xml:space="preserve">5255563</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J117">
-        <v>258</v>
+        <v>868</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763735</t>
+          <t xml:space="preserve">311763694</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Østergade 40C</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255563</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
-        <v>868</v>
+        <v>520</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763694</t>
+          <t xml:space="preserve">311763739</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40C</t>
+          <t xml:space="preserve">Birkholm 7</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,20 +8901,20 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>520</v>
+        <v>4382</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763739</t>
+          <t xml:space="preserve">311764478</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-03</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J120">
-        <v>4382</v>
+        <v>1154</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9056,15 +9056,15 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J121">
-        <v>1154</v>
+        <v>1483</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764478</t>
+          <t xml:space="preserve">311764476</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 7</t>
+          <t xml:space="preserve">Genner Bygade 3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J122">
-        <v>1483</v>
+        <v>1769</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764476</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9206,11 +9206,11 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>1769</v>
+        <v>1063</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -9281,11 +9281,11 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J124">
-        <v>1063</v>
+        <v>275</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genner Bygade 3</t>
+          <t xml:space="preserve">Hovslundvej 12</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,20 +9351,20 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5247379</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>275</v>
+        <v>564</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764474</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9431,11 +9431,11 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J126">
-        <v>564</v>
+        <v>1639</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovslundvej 12</t>
+          <t xml:space="preserve">Østergade 40B</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,20 +9501,20 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247379</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>1639</v>
+        <v>326</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764844</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>326</v>
+        <v>1272</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40B</t>
+          <t xml:space="preserve">Bjerggade 3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5777914</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
-        <v>1272</v>
+        <v>406</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764844</t>
+          <t xml:space="preserve">311766606</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-07</t>
+          <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 3</t>
+          <t xml:space="preserve">Borgmesterløkken 35</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777914</t>
+          <t xml:space="preserve">7861742</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -9735,11 +9735,11 @@
         </is>
       </c>
       <c r="J130">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766606</t>
+          <t xml:space="preserve">311766610</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmesterløkken 35</t>
+          <t xml:space="preserve">Haderslevvej 1</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">7861742</t>
+          <t xml:space="preserve">5780012</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,11 +9810,11 @@
         </is>
       </c>
       <c r="J131">
-        <v>340</v>
+        <v>1126</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766610</t>
+          <t xml:space="preserve">311766629</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haderslevvej 1</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,20 +9876,20 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780012</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J132">
-        <v>1126</v>
+        <v>2585</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766629</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9956,11 +9956,11 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J133">
-        <v>2585</v>
+        <v>1285</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -10031,11 +10031,11 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J134">
-        <v>1285</v>
+        <v>5606</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -10091,30 +10091,30 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Plantagevej 4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">5260532</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>5606</v>
+        <v>4077</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766620</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 4</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260532</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J136">
-        <v>4077</v>
+        <v>1396</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766620</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10256,11 +10256,11 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J137">
-        <v>1396</v>
+        <v>1087</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -10331,11 +10331,11 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J138">
-        <v>1087</v>
+        <v>619</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J139">
-        <v>619</v>
+        <v>354</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766602</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,30 +10466,30 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Vestergade 24A</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">5255997</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766602</t>
+          <t xml:space="preserve">311766615</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 24A</t>
+          <t xml:space="preserve">Østergade 61</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255997</t>
+          <t xml:space="preserve">5254851</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>293</v>
+        <v>1054</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766615</t>
+          <t xml:space="preserve">311766708</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 61</t>
+          <t xml:space="preserve">Østergade 63</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10631,15 +10631,15 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>1054</v>
+        <v>1406</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766708</t>
+          <t xml:space="preserve">311766710</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 63</t>
+          <t xml:space="preserve">Kirkevej 2</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254851</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>1406</v>
+        <v>4747</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766710</t>
+          <t xml:space="preserve">311766871</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-14</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 2</t>
+          <t xml:space="preserve">Padborgvej 55A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J144">
-        <v>4747</v>
+        <v>7373</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -10841,30 +10841,30 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55A</t>
+          <t xml:space="preserve">Kallemosen 18</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5777160</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J145">
-        <v>7373</v>
+        <v>372</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766871</t>
+          <t xml:space="preserve">311767653</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 18</t>
+          <t xml:space="preserve">Kallemosen 20</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>372</v>
+        <v>3627</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 20</t>
+          <t xml:space="preserve">Skovbrynet 10</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777160</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J147">
-        <v>3627</v>
+        <v>2110</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767974</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-19</t>
+          <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11081,15 +11081,15 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J148">
-        <v>2110</v>
+        <v>470</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767974</t>
+          <t xml:space="preserve">311767973</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 10</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11156,15 +11156,15 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J149">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767973</t>
+          <t xml:space="preserve">311767976</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Pilemosen 21</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777457</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>404</v>
+        <v>1635</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767976</t>
+          <t xml:space="preserve">311768984</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-20</t>
+          <t xml:space="preserve">2034-06-25</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilemosen 21</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,20 +11301,20 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777457</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J151">
-        <v>1635</v>
+        <v>542</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768984</t>
+          <t xml:space="preserve">311770633</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-25</t>
+          <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11381,15 +11381,15 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J152">
-        <v>542</v>
+        <v>6116</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770633</t>
+          <t xml:space="preserve">311770634</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J153">
-        <v>6116</v>
+        <v>664</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,30 +11516,30 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Slogsherredsvej 41</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">737562, 5238011</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>664</v>
+        <v>1394</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770634</t>
+          <t xml:space="preserve">311772649</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-02</t>
+          <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11606,15 +11606,15 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J155">
-        <v>1394</v>
+        <v>1287</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772649</t>
+          <t xml:space="preserve">311772650</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 41</t>
+          <t xml:space="preserve">Møllemærsk 24</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">737562, 5238011</t>
+          <t xml:space="preserve">309127, 309128, 309129</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>1287</v>
+        <v>5924</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772650</t>
+          <t xml:space="preserve">311783172</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-10</t>
+          <t xml:space="preserve">2034-09-06</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,40 +11741,40 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemærsk 24</t>
+          <t xml:space="preserve">Vestergade 14</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">309127, 309128, 309129</t>
+          <t xml:space="preserve">5255302</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J157">
-        <v>5924</v>
+        <v>4677</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311783172</t>
+          <t xml:space="preserve">311792061</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-06</t>
+          <t xml:space="preserve">2034-10-17</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,40 +11816,40 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 14</t>
+          <t xml:space="preserve">Kirkeplads 3A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255302</t>
+          <t xml:space="preserve">5774705</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J158">
-        <v>4677</v>
+        <v>408</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792061</t>
+          <t xml:space="preserve">311813570</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-17</t>
+          <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkeplads 3A</t>
+          <t xml:space="preserve">Kirketoften 10</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774705</t>
+          <t xml:space="preserve">5252364</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -11910,11 +11910,11 @@
         </is>
       </c>
       <c r="J159">
-        <v>408</v>
+        <v>325</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813570</t>
+          <t xml:space="preserve">311813574</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 10</t>
+          <t xml:space="preserve">Kirketoften 20</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 20</t>
+          <t xml:space="preserve">Kirketoften 30</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J161">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 30</t>
+          <t xml:space="preserve">Kirketoften 40</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12131,15 +12131,15 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813574</t>
+          <t xml:space="preserve">311813682</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 40</t>
+          <t xml:space="preserve">Kirketoften 50</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 50</t>
+          <t xml:space="preserve">Kirketoften 60</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12281,20 +12281,20 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J164">
-        <v>360</v>
+        <v>1635</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813682</t>
+          <t xml:space="preserve">311813683</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 60</t>
+          <t xml:space="preserve">Rådhusgang 4</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,25 +12351,25 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252364</t>
+          <t xml:space="preserve">5775091</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>1635</v>
+        <v>1235</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813683</t>
+          <t xml:space="preserve">311813583</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgang 4</t>
+          <t xml:space="preserve">Klinkbjerg 34</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775091</t>
+          <t xml:space="preserve">5777878</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>1235</v>
+        <v>308</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813583</t>
+          <t xml:space="preserve">311813806</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-24</t>
+          <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbjerg 34</t>
+          <t xml:space="preserve">Langrode 11</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777878</t>
+          <t xml:space="preserve">5777949</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>308</v>
+        <v>3254</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813806</t>
+          <t xml:space="preserve">311813816</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 11</t>
+          <t xml:space="preserve">Langrode 7A</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12581,15 +12581,15 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J168">
-        <v>3254</v>
+        <v>640</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813816</t>
+          <t xml:space="preserve">311813818</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 7A</t>
+          <t xml:space="preserve">Langrode 9A</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J169">
@@ -12716,40 +12716,40 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 9A</t>
+          <t xml:space="preserve">Harkærvej 13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777949</t>
+          <t xml:space="preserve">737434, 1808354</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J170">
-        <v>640</v>
+        <v>1934</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813818</t>
+          <t xml:space="preserve">311814773</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-25</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12806,11 +12806,11 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J171">
-        <v>1934</v>
+        <v>1343</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J172">
-        <v>1343</v>
+        <v>3168</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,15 +12956,15 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J173">
-        <v>3168</v>
+        <v>895</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814770</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,30 +13016,30 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harkærvej 13</t>
+          <t xml:space="preserve">Sønderborgvej 129</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">737434, 1808354</t>
+          <t xml:space="preserve">737489, 9049653</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J174">
-        <v>895</v>
+        <v>1674</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814770</t>
+          <t xml:space="preserve">311817074</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2035-03-12</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 129</t>
+          <t xml:space="preserve">Løjt Skolegade 27</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,30 +13101,30 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">737489, 9049653</t>
+          <t xml:space="preserve">5253360</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J175">
-        <v>1674</v>
+        <v>858</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311817074</t>
+          <t xml:space="preserve">311821040</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-12</t>
+          <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 27</t>
+          <t xml:space="preserve">Løjt Skolegade 27A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13181,11 +13181,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J176">
-        <v>858</v>
+        <v>256</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 27A</t>
+          <t xml:space="preserve">Nyløkke 17</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,20 +13251,20 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5253360</t>
+          <t xml:space="preserve">5780157</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821040</t>
+          <t xml:space="preserve">311821028</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 17</t>
+          <t xml:space="preserve">Stubbæk Skolegade 1</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,20 +13326,20 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780157</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J178">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821028</t>
+          <t xml:space="preserve">311821030</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 1</t>
+          <t xml:space="preserve">Søstvej 11</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5779435</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J179">
-        <v>373</v>
+        <v>624</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821030</t>
+          <t xml:space="preserve">311821027</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søstvej 11</t>
+          <t xml:space="preserve">Lille Kolstrup 10</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779435</t>
+          <t xml:space="preserve">5779275</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -13485,11 +13485,11 @@
         </is>
       </c>
       <c r="J180">
-        <v>624</v>
+        <v>2117</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821027</t>
+          <t xml:space="preserve">311831284</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-28</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Kolstrup 10</t>
+          <t xml:space="preserve">Nygade 21</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779275</t>
+          <t xml:space="preserve">5774474</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J181">
-        <v>2117</v>
+        <v>1330</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831284</t>
+          <t xml:space="preserve">311831290</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 21</t>
+          <t xml:space="preserve">Nygade 23A</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13631,15 +13631,15 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>1330</v>
+        <v>2030</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831290</t>
+          <t xml:space="preserve">311831286</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23A</t>
+          <t xml:space="preserve">Nygade 23C</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13706,15 +13706,15 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J183">
-        <v>2030</v>
+        <v>1623</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831286</t>
+          <t xml:space="preserve">311831291</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23C</t>
+          <t xml:space="preserve">Nygade 23D</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13781,15 +13781,15 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J184">
-        <v>1623</v>
+        <v>1076</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831291</t>
+          <t xml:space="preserve">311831292</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23D</t>
+          <t xml:space="preserve">Nyløkke 4</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,20 +13851,20 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774474</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J185">
-        <v>1076</v>
+        <v>9062</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831292</t>
+          <t xml:space="preserve">311831238</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 4</t>
+          <t xml:space="preserve">Stubbæk Bygade 1</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,20 +13926,20 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5265560</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J186">
-        <v>9062</v>
+        <v>790</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831238</t>
+          <t xml:space="preserve">311831239</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Bygade 1</t>
+          <t xml:space="preserve">Stubbæk Skolegade 8</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265560</t>
+          <t xml:space="preserve">5265545</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>790</v>
+        <v>666</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831239</t>
+          <t xml:space="preserve">311831237</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 8</t>
+          <t xml:space="preserve">Tøndervej 90</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265545</t>
+          <t xml:space="preserve">5776547</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,11 +14085,11 @@
         </is>
       </c>
       <c r="J188">
-        <v>666</v>
+        <v>2511</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831237</t>
+          <t xml:space="preserve">311831283</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J189">
-        <v>2511</v>
+        <v>4724</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14231,11 +14231,11 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J190">
-        <v>4724</v>
+        <v>490</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J191">
-        <v>490</v>
+        <v>2476</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 90</t>
+          <t xml:space="preserve">Tøndervej 92</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14381,15 +14381,15 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J192">
-        <v>2476</v>
+        <v>762</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831283</t>
+          <t xml:space="preserve">311831294</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 92</t>
+          <t xml:space="preserve">Løjt Skolegade 14</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,20 +14451,20 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776547</t>
+          <t xml:space="preserve">5252489</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>762</v>
+        <v>984</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831294</t>
+          <t xml:space="preserve">311831852</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J194">
-        <v>984</v>
+        <v>1460</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14606,11 +14606,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J195">
-        <v>1460</v>
+        <v>1034</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14681,11 +14681,11 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J196">
-        <v>1034</v>
+        <v>5105</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 14</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 60</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252489</t>
+          <t xml:space="preserve">5775088</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>5105</v>
+        <v>2142</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831852</t>
+          <t xml:space="preserve">311832051</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-14</t>
+          <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14831,11 +14831,11 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J198">
-        <v>2142</v>
+        <v>1062</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14906,11 +14906,11 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J199">
-        <v>1062</v>
+        <v>2149</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 60</t>
+          <t xml:space="preserve">Bjerggade 4E</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,20 +14976,20 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775088</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J200">
-        <v>2149</v>
+        <v>610</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832051</t>
+          <t xml:space="preserve">311848623</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-15</t>
+          <t xml:space="preserve">2035-08-12</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4E</t>
+          <t xml:space="preserve">Bjerggade 4F</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J201">
-        <v>610</v>
+        <v>1113</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848623</t>
+          <t xml:space="preserve">311848622</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4F</t>
+          <t xml:space="preserve">Bjerggade 4G</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15131,15 +15131,15 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J202">
-        <v>1113</v>
+        <v>604</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848622</t>
+          <t xml:space="preserve">311848621</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4G</t>
+          <t xml:space="preserve">Bjerggade 8</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15201,20 +15201,20 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">10202622</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J203">
-        <v>604</v>
+        <v>427</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848621</t>
+          <t xml:space="preserve">311868888</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,17 +15266,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 8</t>
+          <t xml:space="preserve">Nørremarken 44A</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202622</t>
+          <t xml:space="preserve">5243868</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,11 +15285,11 @@
         </is>
       </c>
       <c r="J204">
-        <v>427</v>
+        <v>1263</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868888</t>
+          <t xml:space="preserve">311868866</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44A</t>
+          <t xml:space="preserve">Nørremarken 44C</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243868</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J205">
-        <v>1263</v>
+        <v>1921</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868866</t>
+          <t xml:space="preserve">311868868</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44C</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J206">
-        <v>1921</v>
+        <v>285</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868868</t>
+          <t xml:space="preserve">311868879</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15506,15 +15506,15 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>285</v>
+        <v>805</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868879</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15581,11 +15581,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J208">
-        <v>805</v>
+        <v>650</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15656,11 +15656,11 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J209">
-        <v>650</v>
+        <v>454</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -15716,30 +15716,30 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Skolevænget 33</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>454</v>
+        <v>1429</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868875</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15806,15 +15806,15 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J211">
-        <v>1429</v>
+        <v>860</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868875</t>
+          <t xml:space="preserve">311868877</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,30 +15866,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 33</t>
+          <t xml:space="preserve">Højskolevej 1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">5243526</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>860</v>
+        <v>544</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868877</t>
+          <t xml:space="preserve">311871854</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,30 +15941,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 1</t>
+          <t xml:space="preserve">Bjerggade 4C</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243526</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J213">
-        <v>544</v>
+        <v>891</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871854</t>
+          <t xml:space="preserve">311875341</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4C</t>
+          <t xml:space="preserve">Bladknæk 51</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,20 +16026,20 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">8114886</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J214">
-        <v>891</v>
+        <v>944</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875341</t>
+          <t xml:space="preserve">311875347</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bladknæk 51</t>
+          <t xml:space="preserve">Byvænget 4</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114886</t>
+          <t xml:space="preserve">8052209</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -16110,11 +16110,11 @@
         </is>
       </c>
       <c r="J215">
-        <v>944</v>
+        <v>352</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875347</t>
+          <t xml:space="preserve">311875338</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvænget 4</t>
+          <t xml:space="preserve">Fjordløkke 1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8052209</t>
+          <t xml:space="preserve">5777609</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -16185,11 +16185,11 @@
         </is>
       </c>
       <c r="J216">
-        <v>352</v>
+        <v>540</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875338</t>
+          <t xml:space="preserve">311875336</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordløkke 1</t>
+          <t xml:space="preserve">Langebro 22</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777609</t>
+          <t xml:space="preserve">5776990</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -16260,11 +16260,11 @@
         </is>
       </c>
       <c r="J217">
-        <v>540</v>
+        <v>592</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875336</t>
+          <t xml:space="preserve">311875353</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebro 22</t>
+          <t xml:space="preserve">Lergård 2</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776990</t>
+          <t xml:space="preserve">7681750</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -16335,11 +16335,11 @@
         </is>
       </c>
       <c r="J218">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875353</t>
+          <t xml:space="preserve">311875339</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 2</t>
+          <t xml:space="preserve">Nygade 46</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,7 +16401,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">7681750</t>
+          <t xml:space="preserve">7791737</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -16410,11 +16410,11 @@
         </is>
       </c>
       <c r="J219">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875339</t>
+          <t xml:space="preserve">311875342</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 46</t>
+          <t xml:space="preserve">Nyløkke 2</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,20 +16476,20 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">7791737</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J220">
-        <v>556</v>
+        <v>3204</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875342</t>
+          <t xml:space="preserve">311875333</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 2</t>
+          <t xml:space="preserve">Posekærvej 20</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,20 +16551,20 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5776859</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J221">
-        <v>3204</v>
+        <v>1615</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875333</t>
+          <t xml:space="preserve">311875334</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posekærvej 20</t>
+          <t xml:space="preserve">Præsteskoven 40</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16626,20 +16626,20 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776859</t>
+          <t xml:space="preserve">9392994</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>1615</v>
+        <v>690</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875334</t>
+          <t xml:space="preserve">311875343</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præsteskoven 40</t>
+          <t xml:space="preserve">Sejsbjerg 16</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,20 +16701,20 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">9392994</t>
+          <t xml:space="preserve">8353545</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J223">
-        <v>690</v>
+        <v>741</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875343</t>
+          <t xml:space="preserve">311875345</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejsbjerg 16</t>
+          <t xml:space="preserve">Vestvejen 25</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,20 +16776,20 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">8353545</t>
+          <t xml:space="preserve">5776345</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J224">
-        <v>741</v>
+        <v>1081</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875345</t>
+          <t xml:space="preserve">311875335</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestvejen 25</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776345</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>1081</v>
+        <v>853</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875335</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16931,11 +16931,11 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J226">
-        <v>853</v>
+        <v>1115</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -17006,11 +17006,11 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J227">
-        <v>1115</v>
+        <v>381</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -17081,11 +17081,11 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J228">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -17156,11 +17156,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J229">
-        <v>445</v>
+        <v>925</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -17231,11 +17231,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J230">
-        <v>925</v>
+        <v>405</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -17306,11 +17306,11 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J231">
-        <v>405</v>
+        <v>2453</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -17366,40 +17366,40 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Sandved 45</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5777338</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J232">
-        <v>2453</v>
+        <v>1700</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311886895</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandved 45</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17451,30 +17451,30 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777338</t>
+          <t xml:space="preserve">5776972</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J233">
-        <v>1700</v>
+        <v>6714</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886895</t>
+          <t xml:space="preserve">311888544</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
+          <t xml:space="preserve">Stubbæk Skolegade 3</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776972</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -17535,11 +17535,11 @@
         </is>
       </c>
       <c r="J234">
-        <v>6714</v>
+        <v>1592</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888544</t>
+          <t xml:space="preserve">311888543</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17606,11 +17606,11 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J235">
-        <v>1592</v>
+        <v>723</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>723</v>
+        <v>2411</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17726,12 +17726,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Museum Sønderjylland</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 3</t>
+          <t xml:space="preserve">H P Hanssens Gade 33</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,30 +17751,30 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5776368</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>2411</v>
+        <v>839</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888543</t>
+          <t xml:space="preserve">311929036</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Boligeftersyn Syd ApS</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
